--- a/output/yearly_population_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_63_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6333</v>
+        <v>6331</v>
       </c>
       <c r="C2" t="n">
-        <v>13187</v>
+        <v>10648</v>
       </c>
       <c r="D2" t="n">
-        <v>26118</v>
+        <v>23364</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4121</v>
+        <v>3703</v>
       </c>
       <c r="C3" t="n">
-        <v>5967</v>
+        <v>3927</v>
       </c>
       <c r="D3" t="n">
-        <v>18380</v>
+        <v>14913</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2829</v>
+        <v>2957</v>
       </c>
       <c r="C4" t="n">
-        <v>3486</v>
+        <v>3942</v>
       </c>
       <c r="D4" t="n">
-        <v>9169</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>1976</v>
       </c>
       <c r="C5" t="n">
-        <v>2836</v>
+        <v>3800</v>
       </c>
       <c r="D5" t="n">
-        <v>3558</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1118</v>
+        <v>1187</v>
       </c>
       <c r="C6" t="n">
-        <v>2642</v>
+        <v>3382</v>
       </c>
       <c r="D6" t="n">
-        <v>1355</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="C7" t="n">
-        <v>1785</v>
+        <v>2210</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C8" t="n">
-        <v>853</v>
+        <v>1011</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7564</v>
+        <v>9517</v>
       </c>
       <c r="C2" t="n">
-        <v>9531</v>
+        <v>6385</v>
       </c>
       <c r="D2" t="n">
-        <v>34632</v>
+        <v>21169</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4199</v>
+        <v>3937</v>
       </c>
       <c r="C3" t="n">
-        <v>8138</v>
+        <v>6096</v>
       </c>
       <c r="D3" t="n">
-        <v>18197</v>
+        <v>15060</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2885</v>
+        <v>2830</v>
       </c>
       <c r="C4" t="n">
-        <v>4604</v>
+        <v>3852</v>
       </c>
       <c r="D4" t="n">
-        <v>10393</v>
+        <v>8689</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2029</v>
+        <v>2114</v>
       </c>
       <c r="C5" t="n">
-        <v>3049</v>
+        <v>3748</v>
       </c>
       <c r="D5" t="n">
-        <v>4277</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1321</v>
+        <v>1384</v>
       </c>
       <c r="C6" t="n">
-        <v>2703</v>
+        <v>3500</v>
       </c>
       <c r="D6" t="n">
-        <v>1675</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="C7" t="n">
-        <v>2144</v>
+        <v>2725</v>
       </c>
       <c r="D7" t="n">
-        <v>772</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C8" t="n">
-        <v>1254</v>
+        <v>1505</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9331</v>
+        <v>10323</v>
       </c>
       <c r="C2" t="n">
-        <v>7432</v>
+        <v>12571</v>
       </c>
       <c r="D2" t="n">
-        <v>29713</v>
+        <v>23422</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4517</v>
+        <v>4930</v>
       </c>
       <c r="C3" t="n">
-        <v>7728</v>
+        <v>5517</v>
       </c>
       <c r="D3" t="n">
-        <v>19004</v>
+        <v>14829</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2908</v>
+        <v>2784</v>
       </c>
       <c r="C4" t="n">
-        <v>5990</v>
+        <v>4741</v>
       </c>
       <c r="D4" t="n">
-        <v>11101</v>
+        <v>9258</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2128</v>
+        <v>2137</v>
       </c>
       <c r="C5" t="n">
-        <v>3613</v>
+        <v>3676</v>
       </c>
       <c r="D5" t="n">
-        <v>5027</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1461</v>
+        <v>1527</v>
       </c>
       <c r="C6" t="n">
-        <v>2821</v>
+        <v>3534</v>
       </c>
       <c r="D6" t="n">
-        <v>1986</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>857</v>
+        <v>895</v>
       </c>
       <c r="C7" t="n">
-        <v>2346</v>
+        <v>3035</v>
       </c>
       <c r="D7" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="C8" t="n">
-        <v>1590</v>
+        <v>1955</v>
       </c>
       <c r="D8" t="n">
-        <v>498</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C9" t="n">
-        <v>818</v>
+        <v>962</v>
       </c>
       <c r="D9" t="n">
         <v>330</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>418</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>9360</v>
       </c>
       <c r="C2" t="n">
-        <v>5053</v>
+        <v>8648</v>
       </c>
       <c r="D2" t="n">
-        <v>24500</v>
+        <v>19449</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5363</v>
+        <v>5480</v>
       </c>
       <c r="C3" t="n">
-        <v>10725</v>
+        <v>8661</v>
       </c>
       <c r="D3" t="n">
-        <v>20924</v>
+        <v>16368</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="C4" t="n">
-        <v>6803</v>
+        <v>6123</v>
       </c>
       <c r="D4" t="n">
-        <v>10721</v>
+        <v>9013</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1349</v>
+        <v>1410</v>
       </c>
       <c r="C5" t="n">
-        <v>2764</v>
+        <v>3463</v>
       </c>
       <c r="D5" t="n">
-        <v>3297</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>791</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>2299</v>
+        <v>2974</v>
       </c>
       <c r="D6" t="n">
-        <v>862</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>1558</v>
+        <v>1915</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>801</v>
+        <v>942</v>
       </c>
       <c r="D8" t="n">
         <v>323</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5070</v>
+        <v>5499</v>
       </c>
       <c r="C2" t="n">
-        <v>2534</v>
+        <v>4396</v>
       </c>
       <c r="D2" t="n">
-        <v>17379</v>
+        <v>13642</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5715</v>
+        <v>6076</v>
       </c>
       <c r="C3" t="n">
-        <v>7415</v>
+        <v>7851</v>
       </c>
       <c r="D3" t="n">
-        <v>20405</v>
+        <v>16001</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2809</v>
+        <v>2848</v>
       </c>
       <c r="C4" t="n">
-        <v>8664</v>
+        <v>7400</v>
       </c>
       <c r="D4" t="n">
-        <v>11967</v>
+        <v>9884</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1503</v>
+        <v>1553</v>
       </c>
       <c r="C5" t="n">
-        <v>4506</v>
+        <v>4596</v>
       </c>
       <c r="D5" t="n">
-        <v>4186</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>976</v>
       </c>
       <c r="C6" t="n">
-        <v>2599</v>
+        <v>3324</v>
       </c>
       <c r="D6" t="n">
-        <v>1110</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>1875</v>
+        <v>2344</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>1048</v>
+        <v>1246</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5073</v>
+        <v>5922</v>
       </c>
       <c r="C2" t="n">
-        <v>3808</v>
+        <v>7533</v>
       </c>
       <c r="D2" t="n">
-        <v>22311</v>
+        <v>10989</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4616</v>
+        <v>4945</v>
       </c>
       <c r="C3" t="n">
-        <v>4542</v>
+        <v>5521</v>
       </c>
       <c r="D3" t="n">
-        <v>18622</v>
+        <v>14604</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3456</v>
+        <v>3602</v>
       </c>
       <c r="C4" t="n">
-        <v>7872</v>
+        <v>7466</v>
       </c>
       <c r="D4" t="n">
-        <v>12980</v>
+        <v>10581</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1822</v>
+        <v>1864</v>
       </c>
       <c r="C5" t="n">
-        <v>6368</v>
+        <v>5863</v>
       </c>
       <c r="D5" t="n">
-        <v>5253</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1084</v>
+        <v>1129</v>
       </c>
       <c r="C6" t="n">
-        <v>3459</v>
+        <v>3853</v>
       </c>
       <c r="D6" t="n">
-        <v>1538</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C7" t="n">
-        <v>2204</v>
+        <v>2788</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>1390</v>
+        <v>1698</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>644</v>
+        <v>753</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3017</v>
+        <v>3512</v>
       </c>
       <c r="C2" t="n">
-        <v>1830</v>
+        <v>3510</v>
       </c>
       <c r="D2" t="n">
-        <v>15599</v>
+        <v>7688</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4559</v>
+        <v>4997</v>
       </c>
       <c r="C3" t="n">
-        <v>4157</v>
+        <v>6029</v>
       </c>
       <c r="D3" t="n">
-        <v>18588</v>
+        <v>13900</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3831</v>
+        <v>4003</v>
       </c>
       <c r="C4" t="n">
-        <v>7377</v>
+        <v>7392</v>
       </c>
       <c r="D4" t="n">
-        <v>13746</v>
+        <v>11157</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1907</v>
+        <v>1962</v>
       </c>
       <c r="C5" t="n">
-        <v>7578</v>
+        <v>7056</v>
       </c>
       <c r="D5" t="n">
-        <v>5532</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>907</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>4278</v>
+        <v>4799</v>
       </c>
       <c r="D6" t="n">
-        <v>1490</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>2408</v>
+        <v>3006</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1053</v>
+        <v>1253</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3339</v>
+        <v>4599</v>
       </c>
       <c r="C2" t="n">
-        <v>5190</v>
+        <v>2953</v>
       </c>
       <c r="D2" t="n">
-        <v>16256</v>
+        <v>9414</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3358</v>
+        <v>3748</v>
       </c>
       <c r="C3" t="n">
-        <v>2767</v>
+        <v>4355</v>
       </c>
       <c r="D3" t="n">
-        <v>17110</v>
+        <v>12121</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3603</v>
+        <v>3843</v>
       </c>
       <c r="C4" t="n">
-        <v>5708</v>
+        <v>6597</v>
       </c>
       <c r="D4" t="n">
-        <v>14071</v>
+        <v>11372</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2373</v>
+        <v>2460</v>
       </c>
       <c r="C5" t="n">
-        <v>7402</v>
+        <v>7128</v>
       </c>
       <c r="D5" t="n">
-        <v>6546</v>
+        <v>5494</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1175</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="n">
-        <v>5674</v>
+        <v>5755</v>
       </c>
       <c r="D6" t="n">
-        <v>2013</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C7" t="n">
-        <v>3205</v>
+        <v>3784</v>
       </c>
       <c r="D7" t="n">
-        <v>714</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1564</v>
+        <v>1912</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>618</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2452</v>
+        <v>3115</v>
       </c>
       <c r="C2" t="n">
-        <v>2922</v>
+        <v>1981</v>
       </c>
       <c r="D2" t="n">
-        <v>12996</v>
+        <v>7101</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2937</v>
+        <v>3523</v>
       </c>
       <c r="C3" t="n">
-        <v>3409</v>
+        <v>3487</v>
       </c>
       <c r="D3" t="n">
-        <v>16076</v>
+        <v>11136</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3222</v>
+        <v>3479</v>
       </c>
       <c r="C4" t="n">
-        <v>4513</v>
+        <v>5682</v>
       </c>
       <c r="D4" t="n">
-        <v>14186</v>
+        <v>11236</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2613</v>
+        <v>2730</v>
       </c>
       <c r="C5" t="n">
-        <v>6914</v>
+        <v>7059</v>
       </c>
       <c r="D5" t="n">
-        <v>7339</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1385</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="n">
-        <v>6444</v>
+        <v>6419</v>
       </c>
       <c r="D6" t="n">
-        <v>2419</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>4028</v>
+        <v>4524</v>
       </c>
       <c r="D7" t="n">
-        <v>822</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1979</v>
+        <v>2397</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>629</v>
+        <v>722</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3521</v>
+        <v>4179</v>
       </c>
       <c r="C2" t="n">
-        <v>5719</v>
+        <v>3083</v>
       </c>
       <c r="D2" t="n">
-        <v>15542</v>
+        <v>9279</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2327</v>
+        <v>2843</v>
       </c>
       <c r="C3" t="n">
-        <v>2884</v>
+        <v>2554</v>
       </c>
       <c r="D3" t="n">
-        <v>14677</v>
+        <v>9939</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2712</v>
+        <v>3036</v>
       </c>
       <c r="C4" t="n">
-        <v>3952</v>
+        <v>4615</v>
       </c>
       <c r="D4" t="n">
-        <v>14026</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2599</v>
+        <v>2748</v>
       </c>
       <c r="C5" t="n">
-        <v>5802</v>
+        <v>6343</v>
       </c>
       <c r="D5" t="n">
-        <v>8036</v>
+        <v>6612</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1669</v>
+        <v>1725</v>
       </c>
       <c r="C6" t="n">
-        <v>6570</v>
+        <v>6678</v>
       </c>
       <c r="D6" t="n">
-        <v>2978</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="C7" t="n">
-        <v>4926</v>
+        <v>5227</v>
       </c>
       <c r="D7" t="n">
-        <v>1017</v>
+        <v>942</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>2720</v>
+        <v>3146</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1065</v>
+        <v>1286</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
         <v>140</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6840</v>
+        <v>8097</v>
       </c>
       <c r="C2" t="n">
-        <v>5102</v>
+        <v>8799</v>
       </c>
       <c r="D2" t="n">
-        <v>11710</v>
+        <v>15852</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2522</v>
+        <v>2993</v>
       </c>
       <c r="C2" t="n">
-        <v>3249</v>
+        <v>1751</v>
       </c>
       <c r="D2" t="n">
-        <v>11438</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3147</v>
+        <v>3747</v>
       </c>
       <c r="C3" t="n">
-        <v>3790</v>
+        <v>2897</v>
       </c>
       <c r="D3" t="n">
-        <v>16027</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3785</v>
+        <v>4092</v>
       </c>
       <c r="C4" t="n">
-        <v>5880</v>
+        <v>6648</v>
       </c>
       <c r="D4" t="n">
-        <v>14373</v>
+        <v>11237</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1614</v>
+        <v>1670</v>
       </c>
       <c r="C5" t="n">
-        <v>8938</v>
+        <v>9376</v>
       </c>
       <c r="D5" t="n">
-        <v>7322</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>536</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>6115</v>
+        <v>6431</v>
       </c>
       <c r="D6" t="n">
-        <v>2326</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>2665</v>
+        <v>3083</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1043</v>
+        <v>1260</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
         <v>137</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7510</v>
+        <v>7845</v>
       </c>
       <c r="C2" t="n">
-        <v>9708</v>
+        <v>7453</v>
       </c>
       <c r="D2" t="n">
-        <v>26689</v>
+        <v>20703</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2905</v>
+        <v>3438</v>
       </c>
       <c r="C3" t="n">
-        <v>2571</v>
+        <v>4434</v>
       </c>
       <c r="D3" t="n">
-        <v>2606</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5387</v>
+        <v>5494</v>
       </c>
       <c r="C2" t="n">
-        <v>5452</v>
+        <v>9539</v>
       </c>
       <c r="D2" t="n">
-        <v>37910</v>
+        <v>22575</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4276</v>
+        <v>4636</v>
       </c>
       <c r="C3" t="n">
-        <v>5700</v>
+        <v>5297</v>
       </c>
       <c r="D3" t="n">
-        <v>6460</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1296</v>
+        <v>1528</v>
       </c>
       <c r="C4" t="n">
-        <v>1551</v>
+        <v>2642</v>
       </c>
       <c r="D4" t="n">
-        <v>1706</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5648</v>
+        <v>6092</v>
       </c>
       <c r="C2" t="n">
-        <v>4197</v>
+        <v>6422</v>
       </c>
       <c r="D2" t="n">
-        <v>28711</v>
+        <v>24875</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4006</v>
+        <v>4163</v>
       </c>
       <c r="C3" t="n">
-        <v>4827</v>
+        <v>6561</v>
       </c>
       <c r="D3" t="n">
-        <v>11026</v>
+        <v>8206</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2333</v>
+        <v>2585</v>
       </c>
       <c r="C4" t="n">
-        <v>3828</v>
+        <v>4065</v>
       </c>
       <c r="D4" t="n">
-        <v>2566</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>582</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>930</v>
+        <v>1517</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5356</v>
+        <v>5744</v>
       </c>
       <c r="C2" t="n">
-        <v>3866</v>
+        <v>4715</v>
       </c>
       <c r="D2" t="n">
-        <v>22657</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>4157</v>
       </c>
       <c r="C3" t="n">
-        <v>3931</v>
+        <v>5660</v>
       </c>
       <c r="D3" t="n">
-        <v>12937</v>
+        <v>10161</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2663</v>
+        <v>2864</v>
       </c>
       <c r="C4" t="n">
-        <v>4239</v>
+        <v>5298</v>
       </c>
       <c r="D4" t="n">
-        <v>4031</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1200</v>
+        <v>1324</v>
       </c>
       <c r="C5" t="n">
-        <v>2412</v>
+        <v>2767</v>
       </c>
       <c r="D5" t="n">
-        <v>1421</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>613</v>
+        <v>907</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6339</v>
+        <v>6784</v>
       </c>
       <c r="C2" t="n">
-        <v>3317</v>
+        <v>4170</v>
       </c>
       <c r="D2" t="n">
-        <v>35213</v>
+        <v>28906</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3362</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>3196</v>
+        <v>4252</v>
       </c>
       <c r="D3" t="n">
-        <v>12705</v>
+        <v>10971</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2045</v>
+        <v>2152</v>
       </c>
       <c r="C4" t="n">
-        <v>3299</v>
+        <v>4494</v>
       </c>
       <c r="D4" t="n">
-        <v>4829</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>999</v>
+        <v>1092</v>
       </c>
       <c r="C5" t="n">
-        <v>2453</v>
+        <v>2941</v>
       </c>
       <c r="D5" t="n">
-        <v>1470</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="C6" t="n">
-        <v>1007</v>
+        <v>1229</v>
       </c>
       <c r="D6" t="n">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>393</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5707</v>
+        <v>5824</v>
       </c>
       <c r="C2" t="n">
-        <v>6559</v>
+        <v>6117</v>
       </c>
       <c r="D2" t="n">
-        <v>34237</v>
+        <v>27645</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4011</v>
+        <v>4282</v>
       </c>
       <c r="C3" t="n">
-        <v>2806</v>
+        <v>3619</v>
       </c>
       <c r="D3" t="n">
-        <v>15551</v>
+        <v>13176</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2343</v>
+        <v>2498</v>
       </c>
       <c r="C4" t="n">
-        <v>3168</v>
+        <v>4256</v>
       </c>
       <c r="D4" t="n">
-        <v>6223</v>
+        <v>5315</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1359</v>
+        <v>1431</v>
       </c>
       <c r="C5" t="n">
-        <v>2897</v>
+        <v>3774</v>
       </c>
       <c r="D5" t="n">
-        <v>2102</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>626</v>
+        <v>683</v>
       </c>
       <c r="C6" t="n">
-        <v>1813</v>
+        <v>2155</v>
       </c>
       <c r="D6" t="n">
-        <v>906</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="C7" t="n">
-        <v>697</v>
+        <v>859</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6268</v>
+        <v>4920</v>
       </c>
       <c r="C2" t="n">
-        <v>9548</v>
+        <v>4690</v>
       </c>
       <c r="D2" t="n">
-        <v>32407</v>
+        <v>24068</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3980</v>
+        <v>4133</v>
       </c>
       <c r="C3" t="n">
-        <v>4174</v>
+        <v>4297</v>
       </c>
       <c r="D3" t="n">
-        <v>17421</v>
+        <v>14542</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2732</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>2870</v>
+        <v>3812</v>
       </c>
       <c r="D4" t="n">
-        <v>7824</v>
+        <v>6662</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1616</v>
+        <v>1706</v>
       </c>
       <c r="C5" t="n">
-        <v>2985</v>
+        <v>3954</v>
       </c>
       <c r="D5" t="n">
-        <v>2769</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>948</v>
       </c>
       <c r="C6" t="n">
-        <v>2364</v>
+        <v>2970</v>
       </c>
       <c r="D6" t="n">
-        <v>1111</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="C7" t="n">
-        <v>1276</v>
+        <v>1510</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>479</v>
+        <v>586</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_63_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6331</v>
+        <v>8587</v>
       </c>
       <c r="C2" t="n">
-        <v>10648</v>
+        <v>6147</v>
       </c>
       <c r="D2" t="n">
-        <v>23364</v>
+        <v>36695</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>5159</v>
       </c>
       <c r="C3" t="n">
-        <v>3927</v>
+        <v>5978</v>
       </c>
       <c r="D3" t="n">
-        <v>14913</v>
+        <v>14137</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2957</v>
+        <v>4174</v>
       </c>
       <c r="C4" t="n">
-        <v>3942</v>
+        <v>7123</v>
       </c>
       <c r="D4" t="n">
-        <v>7757</v>
+        <v>6752</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1976</v>
+        <v>2550</v>
       </c>
       <c r="C5" t="n">
-        <v>3800</v>
+        <v>5056</v>
       </c>
       <c r="D5" t="n">
-        <v>3098</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1187</v>
+        <v>1332</v>
       </c>
       <c r="C6" t="n">
-        <v>3382</v>
+        <v>2468</v>
       </c>
       <c r="D6" t="n">
-        <v>1254</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>573</v>
+        <v>625</v>
       </c>
       <c r="C7" t="n">
-        <v>2210</v>
+        <v>1302</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>616</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9517</v>
+        <v>9601</v>
       </c>
       <c r="C2" t="n">
-        <v>6385</v>
+        <v>10511</v>
       </c>
       <c r="D2" t="n">
-        <v>21169</v>
+        <v>27470</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3937</v>
+        <v>5409</v>
       </c>
       <c r="C3" t="n">
-        <v>6096</v>
+        <v>5336</v>
       </c>
       <c r="D3" t="n">
-        <v>15060</v>
+        <v>16254</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2830</v>
+        <v>3935</v>
       </c>
       <c r="C4" t="n">
-        <v>3852</v>
+        <v>6367</v>
       </c>
       <c r="D4" t="n">
-        <v>8689</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2114</v>
+        <v>2883</v>
       </c>
       <c r="C5" t="n">
-        <v>3748</v>
+        <v>5903</v>
       </c>
       <c r="D5" t="n">
-        <v>3689</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1384</v>
+        <v>1670</v>
       </c>
       <c r="C6" t="n">
-        <v>3500</v>
+        <v>3562</v>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>744</v>
+        <v>824</v>
       </c>
       <c r="C7" t="n">
-        <v>2725</v>
+        <v>1815</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C8" t="n">
-        <v>1505</v>
+        <v>898</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10323</v>
+        <v>11852</v>
       </c>
       <c r="C2" t="n">
-        <v>12571</v>
+        <v>12679</v>
       </c>
       <c r="D2" t="n">
-        <v>23422</v>
+        <v>21291</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4930</v>
+        <v>5745</v>
       </c>
       <c r="C3" t="n">
-        <v>5517</v>
+        <v>6601</v>
       </c>
       <c r="D3" t="n">
-        <v>14829</v>
+        <v>16559</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2784</v>
+        <v>3850</v>
       </c>
       <c r="C4" t="n">
-        <v>4741</v>
+        <v>5789</v>
       </c>
       <c r="D4" t="n">
-        <v>9258</v>
+        <v>8665</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2137</v>
+        <v>2938</v>
       </c>
       <c r="C5" t="n">
-        <v>3676</v>
+        <v>5915</v>
       </c>
       <c r="D5" t="n">
-        <v>4296</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1527</v>
+        <v>1950</v>
       </c>
       <c r="C6" t="n">
-        <v>3534</v>
+        <v>4439</v>
       </c>
       <c r="D6" t="n">
-        <v>1776</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>895</v>
+        <v>1034</v>
       </c>
       <c r="C7" t="n">
-        <v>3035</v>
+        <v>2516</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="C8" t="n">
-        <v>1955</v>
+        <v>1239</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C9" t="n">
-        <v>962</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>418</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
         <v>166</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9360</v>
+        <v>10768</v>
       </c>
       <c r="C2" t="n">
-        <v>8648</v>
+        <v>8723</v>
       </c>
       <c r="D2" t="n">
-        <v>19449</v>
+        <v>17827</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5480</v>
+        <v>6902</v>
       </c>
       <c r="C3" t="n">
-        <v>8661</v>
+        <v>10146</v>
       </c>
       <c r="D3" t="n">
-        <v>16368</v>
+        <v>17763</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1974</v>
+        <v>2714</v>
       </c>
       <c r="C4" t="n">
-        <v>6123</v>
+        <v>8846</v>
       </c>
       <c r="D4" t="n">
-        <v>9013</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1410</v>
+        <v>1801</v>
       </c>
       <c r="C5" t="n">
-        <v>3463</v>
+        <v>4350</v>
       </c>
       <c r="D5" t="n">
-        <v>2895</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>955</v>
       </c>
       <c r="C6" t="n">
-        <v>2974</v>
+        <v>2465</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>1915</v>
+        <v>1214</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>942</v>
+        <v>584</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>162</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>122</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5499</v>
+        <v>6529</v>
       </c>
       <c r="C2" t="n">
-        <v>4396</v>
+        <v>4320</v>
       </c>
       <c r="D2" t="n">
-        <v>13642</v>
+        <v>12628</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6076</v>
+        <v>7326</v>
       </c>
       <c r="C3" t="n">
-        <v>7851</v>
+        <v>8623</v>
       </c>
       <c r="D3" t="n">
-        <v>16001</v>
+        <v>16748</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2848</v>
+        <v>3733</v>
       </c>
       <c r="C4" t="n">
-        <v>7400</v>
+        <v>9515</v>
       </c>
       <c r="D4" t="n">
-        <v>9884</v>
+        <v>9668</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1553</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>4596</v>
+        <v>6324</v>
       </c>
       <c r="D5" t="n">
-        <v>3626</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>976</v>
+        <v>1142</v>
       </c>
       <c r="C6" t="n">
-        <v>3324</v>
+        <v>3266</v>
       </c>
       <c r="D6" t="n">
-        <v>1036</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>2344</v>
+        <v>1639</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>780</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5922</v>
+        <v>7501</v>
       </c>
       <c r="C2" t="n">
-        <v>7533</v>
+        <v>10421</v>
       </c>
       <c r="D2" t="n">
-        <v>10989</v>
+        <v>15995</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4945</v>
+        <v>5876</v>
       </c>
       <c r="C3" t="n">
-        <v>5521</v>
+        <v>5818</v>
       </c>
       <c r="D3" t="n">
-        <v>14604</v>
+        <v>15062</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3602</v>
+        <v>4499</v>
       </c>
       <c r="C4" t="n">
-        <v>7466</v>
+        <v>8880</v>
       </c>
       <c r="D4" t="n">
-        <v>10581</v>
+        <v>10529</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1864</v>
+        <v>2437</v>
       </c>
       <c r="C5" t="n">
-        <v>5863</v>
+        <v>7754</v>
       </c>
       <c r="D5" t="n">
-        <v>4476</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1129</v>
+        <v>1391</v>
       </c>
       <c r="C6" t="n">
-        <v>3853</v>
+        <v>4585</v>
       </c>
       <c r="D6" t="n">
-        <v>1395</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>605</v>
       </c>
       <c r="C7" t="n">
-        <v>2788</v>
+        <v>2355</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C8" t="n">
-        <v>1698</v>
+        <v>1132</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>753</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3512</v>
+        <v>4516</v>
       </c>
       <c r="C2" t="n">
-        <v>3510</v>
+        <v>4948</v>
       </c>
       <c r="D2" t="n">
-        <v>7688</v>
+        <v>11165</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4997</v>
+        <v>6035</v>
       </c>
       <c r="C3" t="n">
-        <v>6029</v>
+        <v>7104</v>
       </c>
       <c r="D3" t="n">
-        <v>13900</v>
+        <v>14821</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4003</v>
+        <v>4956</v>
       </c>
       <c r="C4" t="n">
-        <v>7392</v>
+        <v>8633</v>
       </c>
       <c r="D4" t="n">
-        <v>11157</v>
+        <v>11146</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1962</v>
+        <v>2511</v>
       </c>
       <c r="C5" t="n">
-        <v>7056</v>
+        <v>9131</v>
       </c>
       <c r="D5" t="n">
-        <v>4709</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="n">
-        <v>4799</v>
+        <v>5357</v>
       </c>
       <c r="D6" t="n">
-        <v>1361</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>3006</v>
+        <v>2311</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1253</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4599</v>
+        <v>5504</v>
       </c>
       <c r="C2" t="n">
-        <v>2953</v>
+        <v>5193</v>
       </c>
       <c r="D2" t="n">
-        <v>9414</v>
+        <v>11627</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3748</v>
+        <v>4581</v>
       </c>
       <c r="C3" t="n">
-        <v>4355</v>
+        <v>5485</v>
       </c>
       <c r="D3" t="n">
-        <v>12121</v>
+        <v>13470</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3843</v>
+        <v>4749</v>
       </c>
       <c r="C4" t="n">
-        <v>6597</v>
+        <v>7748</v>
       </c>
       <c r="D4" t="n">
-        <v>11372</v>
+        <v>11371</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2460</v>
+        <v>3078</v>
       </c>
       <c r="C5" t="n">
-        <v>7128</v>
+        <v>8808</v>
       </c>
       <c r="D5" t="n">
-        <v>5494</v>
+        <v>5255</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>1478</v>
       </c>
       <c r="C6" t="n">
-        <v>5755</v>
+        <v>6919</v>
       </c>
       <c r="D6" t="n">
-        <v>1793</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>3784</v>
+        <v>3549</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1912</v>
+        <v>1373</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>618</v>
+        <v>445</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3115</v>
+        <v>3975</v>
       </c>
       <c r="C2" t="n">
-        <v>1981</v>
+        <v>3051</v>
       </c>
       <c r="D2" t="n">
-        <v>7101</v>
+        <v>9049</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3523</v>
+        <v>4268</v>
       </c>
       <c r="C3" t="n">
-        <v>3487</v>
+        <v>4934</v>
       </c>
       <c r="D3" t="n">
-        <v>11136</v>
+        <v>12645</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3479</v>
+        <v>4287</v>
       </c>
       <c r="C4" t="n">
-        <v>5682</v>
+        <v>6844</v>
       </c>
       <c r="D4" t="n">
-        <v>11236</v>
+        <v>11396</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2730</v>
+        <v>3392</v>
       </c>
       <c r="C5" t="n">
-        <v>7059</v>
+        <v>8586</v>
       </c>
       <c r="D5" t="n">
-        <v>6109</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1438</v>
+        <v>1740</v>
       </c>
       <c r="C6" t="n">
-        <v>6419</v>
+        <v>7774</v>
       </c>
       <c r="D6" t="n">
-        <v>2126</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C7" t="n">
-        <v>4524</v>
+        <v>4583</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2397</v>
+        <v>1835</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>722</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4179</v>
+        <v>5487</v>
       </c>
       <c r="C2" t="n">
-        <v>3083</v>
+        <v>9659</v>
       </c>
       <c r="D2" t="n">
-        <v>9279</v>
+        <v>12328</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2843</v>
+        <v>3508</v>
       </c>
       <c r="C3" t="n">
-        <v>2554</v>
+        <v>3749</v>
       </c>
       <c r="D3" t="n">
-        <v>9939</v>
+        <v>11525</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3036</v>
+        <v>3719</v>
       </c>
       <c r="C4" t="n">
-        <v>4615</v>
+        <v>5913</v>
       </c>
       <c r="D4" t="n">
-        <v>10880</v>
+        <v>11108</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2748</v>
+        <v>3399</v>
       </c>
       <c r="C5" t="n">
-        <v>6343</v>
+        <v>7721</v>
       </c>
       <c r="D5" t="n">
-        <v>6612</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1725</v>
+        <v>2113</v>
       </c>
       <c r="C6" t="n">
-        <v>6678</v>
+        <v>8014</v>
       </c>
       <c r="D6" t="n">
-        <v>2575</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>618</v>
+        <v>686</v>
       </c>
       <c r="C7" t="n">
-        <v>5227</v>
+        <v>5738</v>
       </c>
       <c r="D7" t="n">
-        <v>942</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>3146</v>
+        <v>2794</v>
       </c>
       <c r="D8" t="n">
         <v>446</v>
@@ -3680,10 +3680,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1286</v>
+        <v>933</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3739,7 +3739,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3781,7 +3781,7 @@
         <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8097</v>
+        <v>8181</v>
       </c>
       <c r="C2" t="n">
-        <v>8799</v>
+        <v>3283</v>
       </c>
       <c r="D2" t="n">
-        <v>15852</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2993</v>
+        <v>3972</v>
       </c>
       <c r="C2" t="n">
-        <v>1751</v>
+        <v>5641</v>
       </c>
       <c r="D2" t="n">
-        <v>6830</v>
+        <v>9172</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3747</v>
+        <v>4663</v>
       </c>
       <c r="C3" t="n">
-        <v>2897</v>
+        <v>5361</v>
       </c>
       <c r="D3" t="n">
-        <v>10866</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4092</v>
+        <v>5010</v>
       </c>
       <c r="C4" t="n">
-        <v>6648</v>
+        <v>8520</v>
       </c>
       <c r="D4" t="n">
-        <v>11237</v>
+        <v>11445</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1670</v>
+        <v>2015</v>
       </c>
       <c r="C5" t="n">
-        <v>9376</v>
+        <v>11253</v>
       </c>
       <c r="D5" t="n">
-        <v>6085</v>
+        <v>5815</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>633</v>
       </c>
       <c r="C6" t="n">
-        <v>6431</v>
+        <v>7115</v>
       </c>
       <c r="D6" t="n">
-        <v>2064</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>3083</v>
+        <v>2738</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1260</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4389,7 +4389,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7845</v>
+        <v>8090</v>
       </c>
       <c r="C2" t="n">
-        <v>7453</v>
+        <v>5773</v>
       </c>
       <c r="D2" t="n">
-        <v>20703</v>
+        <v>25803</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3438</v>
+        <v>3474</v>
       </c>
       <c r="C3" t="n">
-        <v>4434</v>
+        <v>1680</v>
       </c>
       <c r="D3" t="n">
-        <v>3302</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5494</v>
+        <v>6155</v>
       </c>
       <c r="C2" t="n">
-        <v>9539</v>
+        <v>4551</v>
       </c>
       <c r="D2" t="n">
-        <v>22575</v>
+        <v>26387</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4636</v>
+        <v>4751</v>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>3446</v>
       </c>
       <c r="D3" t="n">
-        <v>5982</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="C4" t="n">
-        <v>2642</v>
+        <v>1028</v>
       </c>
       <c r="D4" t="n">
-        <v>1846</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6092</v>
+        <v>6047</v>
       </c>
       <c r="C2" t="n">
-        <v>6422</v>
+        <v>4953</v>
       </c>
       <c r="D2" t="n">
-        <v>24875</v>
+        <v>20670</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4163</v>
+        <v>4477</v>
       </c>
       <c r="C3" t="n">
-        <v>6561</v>
+        <v>3504</v>
       </c>
       <c r="D3" t="n">
-        <v>8206</v>
+        <v>8254</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2585</v>
+        <v>2667</v>
       </c>
       <c r="C4" t="n">
-        <v>4065</v>
+        <v>2376</v>
       </c>
       <c r="D4" t="n">
-        <v>2583</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>1517</v>
+        <v>657</v>
       </c>
       <c r="D5" t="n">
-        <v>1279</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,10 +5302,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5744</v>
+        <v>8602</v>
       </c>
       <c r="C2" t="n">
-        <v>4715</v>
+        <v>8854</v>
       </c>
       <c r="D2" t="n">
-        <v>24741</v>
+        <v>19158</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4157</v>
+        <v>4295</v>
       </c>
       <c r="C3" t="n">
-        <v>5660</v>
+        <v>3699</v>
       </c>
       <c r="D3" t="n">
-        <v>10161</v>
+        <v>9560</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2864</v>
+        <v>3042</v>
       </c>
       <c r="C4" t="n">
-        <v>5298</v>
+        <v>2910</v>
       </c>
       <c r="D4" t="n">
-        <v>3530</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1324</v>
+        <v>1380</v>
       </c>
       <c r="C5" t="n">
-        <v>2767</v>
+        <v>1550</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C6" t="n">
-        <v>907</v>
+        <v>478</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6784</v>
+        <v>10107</v>
       </c>
       <c r="C2" t="n">
-        <v>4170</v>
+        <v>14499</v>
       </c>
       <c r="D2" t="n">
-        <v>28906</v>
+        <v>22871</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>4694</v>
       </c>
       <c r="C3" t="n">
-        <v>4252</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="n">
-        <v>10971</v>
+        <v>9734</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2152</v>
+        <v>2263</v>
       </c>
       <c r="C4" t="n">
-        <v>4494</v>
+        <v>2718</v>
       </c>
       <c r="D4" t="n">
-        <v>4041</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1092</v>
+        <v>1153</v>
       </c>
       <c r="C5" t="n">
-        <v>2941</v>
+        <v>1659</v>
       </c>
       <c r="D5" t="n">
-        <v>1431</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="C6" t="n">
-        <v>1229</v>
+        <v>682</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>393</v>
+        <v>265</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5824</v>
+        <v>8464</v>
       </c>
       <c r="C2" t="n">
-        <v>6117</v>
+        <v>8620</v>
       </c>
       <c r="D2" t="n">
-        <v>27645</v>
+        <v>21153</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4282</v>
+        <v>6165</v>
       </c>
       <c r="C3" t="n">
-        <v>3619</v>
+        <v>9216</v>
       </c>
       <c r="D3" t="n">
-        <v>13176</v>
+        <v>11314</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2498</v>
+        <v>3064</v>
       </c>
       <c r="C4" t="n">
-        <v>4256</v>
+        <v>4179</v>
       </c>
       <c r="D4" t="n">
-        <v>5315</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1431</v>
+        <v>1516</v>
       </c>
       <c r="C5" t="n">
-        <v>3774</v>
+        <v>2254</v>
       </c>
       <c r="D5" t="n">
-        <v>1874</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>683</v>
+        <v>731</v>
       </c>
       <c r="C6" t="n">
-        <v>2155</v>
+        <v>1236</v>
       </c>
       <c r="D6" t="n">
-        <v>891</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>859</v>
+        <v>501</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>314</v>
+        <v>246</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>130</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4920</v>
+        <v>6527</v>
       </c>
       <c r="C2" t="n">
-        <v>4690</v>
+        <v>5972</v>
       </c>
       <c r="D2" t="n">
-        <v>24068</v>
+        <v>32179</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4133</v>
+        <v>5996</v>
       </c>
       <c r="C3" t="n">
-        <v>4297</v>
+        <v>7696</v>
       </c>
       <c r="D3" t="n">
-        <v>14542</v>
+        <v>12073</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>3931</v>
       </c>
       <c r="C4" t="n">
-        <v>3812</v>
+        <v>6945</v>
       </c>
       <c r="D4" t="n">
-        <v>6662</v>
+        <v>5928</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1706</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>3954</v>
+        <v>3238</v>
       </c>
       <c r="D5" t="n">
-        <v>2444</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>1015</v>
       </c>
       <c r="C6" t="n">
-        <v>2970</v>
+        <v>1768</v>
       </c>
       <c r="D6" t="n">
-        <v>1039</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="C7" t="n">
-        <v>1510</v>
+        <v>889</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>586</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_63_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8587</v>
+        <v>1306</v>
       </c>
       <c r="C2" t="n">
-        <v>6147</v>
+        <v>2401</v>
       </c>
       <c r="D2" t="n">
-        <v>36695</v>
+        <v>13448</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5159</v>
+        <v>2133</v>
       </c>
       <c r="C3" t="n">
-        <v>5978</v>
+        <v>6468</v>
       </c>
       <c r="D3" t="n">
-        <v>14137</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4174</v>
+        <v>1274</v>
       </c>
       <c r="C4" t="n">
-        <v>7123</v>
+        <v>8913</v>
       </c>
       <c r="D4" t="n">
-        <v>6752</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2550</v>
+        <v>506</v>
       </c>
       <c r="C5" t="n">
-        <v>5056</v>
+        <v>5491</v>
       </c>
       <c r="D5" t="n">
-        <v>2803</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1332</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>2468</v>
+        <v>2192</v>
       </c>
       <c r="D6" t="n">
-        <v>1178</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>625</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1302</v>
+        <v>702</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>616</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9601</v>
+        <v>1822</v>
       </c>
       <c r="C2" t="n">
-        <v>10511</v>
+        <v>6470</v>
       </c>
       <c r="D2" t="n">
-        <v>27470</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5409</v>
+        <v>1482</v>
       </c>
       <c r="C3" t="n">
-        <v>5336</v>
+        <v>3784</v>
       </c>
       <c r="D3" t="n">
-        <v>16254</v>
+        <v>10509</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3935</v>
+        <v>1443</v>
       </c>
       <c r="C4" t="n">
-        <v>6367</v>
+        <v>7389</v>
       </c>
       <c r="D4" t="n">
-        <v>7751</v>
+        <v>5674</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2883</v>
+        <v>758</v>
       </c>
       <c r="C5" t="n">
-        <v>5903</v>
+        <v>7236</v>
       </c>
       <c r="D5" t="n">
-        <v>3297</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1670</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>3562</v>
+        <v>3836</v>
       </c>
       <c r="D6" t="n">
-        <v>1411</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>824</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>1815</v>
+        <v>1424</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>898</v>
+        <v>506</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11852</v>
+        <v>964</v>
       </c>
       <c r="C2" t="n">
-        <v>12679</v>
+        <v>2671</v>
       </c>
       <c r="D2" t="n">
-        <v>21291</v>
+        <v>7185</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5745</v>
+        <v>1518</v>
       </c>
       <c r="C3" t="n">
-        <v>6601</v>
+        <v>4679</v>
       </c>
       <c r="D3" t="n">
-        <v>16559</v>
+        <v>10243</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3850</v>
+        <v>1574</v>
       </c>
       <c r="C4" t="n">
-        <v>5789</v>
+        <v>6596</v>
       </c>
       <c r="D4" t="n">
-        <v>8665</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2938</v>
+        <v>742</v>
       </c>
       <c r="C5" t="n">
-        <v>5915</v>
+        <v>8099</v>
       </c>
       <c r="D5" t="n">
-        <v>3838</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1950</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>4439</v>
+        <v>4969</v>
       </c>
       <c r="D6" t="n">
-        <v>1632</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1034</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2516</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>471</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1239</v>
+        <v>486</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10768</v>
+        <v>792</v>
       </c>
       <c r="C2" t="n">
-        <v>8723</v>
+        <v>6401</v>
       </c>
       <c r="D2" t="n">
-        <v>17827</v>
+        <v>7466</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6902</v>
+        <v>1079</v>
       </c>
       <c r="C3" t="n">
-        <v>10146</v>
+        <v>3217</v>
       </c>
       <c r="D3" t="n">
-        <v>17763</v>
+        <v>9155</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2714</v>
+        <v>1373</v>
       </c>
       <c r="C4" t="n">
-        <v>8846</v>
+        <v>5509</v>
       </c>
       <c r="D4" t="n">
-        <v>8309</v>
+        <v>6857</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1801</v>
+        <v>975</v>
       </c>
       <c r="C5" t="n">
-        <v>4350</v>
+        <v>7257</v>
       </c>
       <c r="D5" t="n">
-        <v>2631</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955</v>
+        <v>415</v>
       </c>
       <c r="C6" t="n">
-        <v>2465</v>
+        <v>6439</v>
       </c>
       <c r="D6" t="n">
-        <v>790</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>1214</v>
+        <v>2999</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>584</v>
+        <v>849</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6529</v>
+        <v>445</v>
       </c>
       <c r="C2" t="n">
-        <v>4320</v>
+        <v>3835</v>
       </c>
       <c r="D2" t="n">
-        <v>12628</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7326</v>
+        <v>850</v>
       </c>
       <c r="C3" t="n">
-        <v>8623</v>
+        <v>4217</v>
       </c>
       <c r="D3" t="n">
-        <v>16748</v>
+        <v>8397</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3733</v>
+        <v>1175</v>
       </c>
       <c r="C4" t="n">
-        <v>9515</v>
+        <v>4444</v>
       </c>
       <c r="D4" t="n">
-        <v>9668</v>
+        <v>7133</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="n">
-        <v>6324</v>
+        <v>6716</v>
       </c>
       <c r="D5" t="n">
-        <v>3310</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1142</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>3266</v>
+        <v>6994</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>1639</v>
+        <v>4214</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>780</v>
+        <v>1374</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>338</v>
+        <v>440</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7501</v>
+        <v>610</v>
       </c>
       <c r="C2" t="n">
-        <v>10421</v>
+        <v>12126</v>
       </c>
       <c r="D2" t="n">
-        <v>15995</v>
+        <v>8760</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5876</v>
+        <v>576</v>
       </c>
       <c r="C3" t="n">
-        <v>5818</v>
+        <v>3588</v>
       </c>
       <c r="D3" t="n">
-        <v>15062</v>
+        <v>7396</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4499</v>
+        <v>917</v>
       </c>
       <c r="C4" t="n">
-        <v>8880</v>
+        <v>4242</v>
       </c>
       <c r="D4" t="n">
-        <v>10529</v>
+        <v>7122</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2437</v>
+        <v>1009</v>
       </c>
       <c r="C5" t="n">
-        <v>7754</v>
+        <v>5529</v>
       </c>
       <c r="D5" t="n">
-        <v>4185</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1391</v>
+        <v>676</v>
       </c>
       <c r="C6" t="n">
-        <v>4585</v>
+        <v>6872</v>
       </c>
       <c r="D6" t="n">
-        <v>1302</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>605</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>2355</v>
+        <v>5383</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1132</v>
+        <v>2528</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>791</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4516</v>
+        <v>409</v>
       </c>
       <c r="C2" t="n">
-        <v>4948</v>
+        <v>6305</v>
       </c>
       <c r="D2" t="n">
-        <v>11165</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6035</v>
+        <v>826</v>
       </c>
       <c r="C3" t="n">
-        <v>7104</v>
+        <v>6254</v>
       </c>
       <c r="D3" t="n">
-        <v>14821</v>
+        <v>8142</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4956</v>
+        <v>1390</v>
       </c>
       <c r="C4" t="n">
-        <v>8633</v>
+        <v>6090</v>
       </c>
       <c r="D4" t="n">
-        <v>11146</v>
+        <v>7362</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2511</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>9131</v>
+        <v>8925</v>
       </c>
       <c r="D5" t="n">
-        <v>4421</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>5357</v>
+        <v>6958</v>
       </c>
       <c r="D6" t="n">
-        <v>1276</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>2311</v>
+        <v>2477</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>775</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5504</v>
+        <v>233</v>
       </c>
       <c r="C2" t="n">
-        <v>5193</v>
+        <v>4189</v>
       </c>
       <c r="D2" t="n">
-        <v>11627</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4581</v>
+        <v>550</v>
       </c>
       <c r="C3" t="n">
-        <v>5485</v>
+        <v>5529</v>
       </c>
       <c r="D3" t="n">
-        <v>13470</v>
+        <v>7294</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4749</v>
+        <v>942</v>
       </c>
       <c r="C4" t="n">
-        <v>7748</v>
+        <v>5859</v>
       </c>
       <c r="D4" t="n">
-        <v>11371</v>
+        <v>6977</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3078</v>
+        <v>690</v>
       </c>
       <c r="C5" t="n">
-        <v>8808</v>
+        <v>6669</v>
       </c>
       <c r="D5" t="n">
-        <v>5255</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1478</v>
+        <v>237</v>
       </c>
       <c r="C6" t="n">
-        <v>6919</v>
+        <v>6492</v>
       </c>
       <c r="D6" t="n">
-        <v>1682</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>3549</v>
+        <v>3174</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>923</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3975</v>
+        <v>357</v>
       </c>
       <c r="C2" t="n">
-        <v>3051</v>
+        <v>4056</v>
       </c>
       <c r="D2" t="n">
-        <v>9049</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4268</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>4153</v>
       </c>
       <c r="D3" t="n">
-        <v>12645</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4287</v>
+        <v>666</v>
       </c>
       <c r="C4" t="n">
-        <v>6844</v>
+        <v>5606</v>
       </c>
       <c r="D4" t="n">
-        <v>11396</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3392</v>
+        <v>724</v>
       </c>
       <c r="C5" t="n">
-        <v>8586</v>
+        <v>6094</v>
       </c>
       <c r="D5" t="n">
-        <v>5791</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1740</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
-        <v>7774</v>
+        <v>6574</v>
       </c>
       <c r="D6" t="n">
-        <v>2019</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>4583</v>
+        <v>4862</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1835</v>
+        <v>1990</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5487</v>
+        <v>471</v>
       </c>
       <c r="C2" t="n">
-        <v>9659</v>
+        <v>9715</v>
       </c>
       <c r="D2" t="n">
-        <v>12328</v>
+        <v>9981</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3508</v>
+        <v>288</v>
       </c>
       <c r="C3" t="n">
-        <v>3749</v>
+        <v>3586</v>
       </c>
       <c r="D3" t="n">
-        <v>11525</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3719</v>
+        <v>449</v>
       </c>
       <c r="C4" t="n">
-        <v>5913</v>
+        <v>4736</v>
       </c>
       <c r="D4" t="n">
-        <v>11108</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3399</v>
+        <v>638</v>
       </c>
       <c r="C5" t="n">
-        <v>7721</v>
+        <v>5723</v>
       </c>
       <c r="D5" t="n">
-        <v>6368</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2113</v>
+        <v>502</v>
       </c>
       <c r="C6" t="n">
-        <v>8014</v>
+        <v>6275</v>
       </c>
       <c r="D6" t="n">
-        <v>2463</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>686</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>5738</v>
+        <v>5665</v>
       </c>
       <c r="D7" t="n">
-        <v>882</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2794</v>
+        <v>3283</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>933</v>
+        <v>1181</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8181</v>
+        <v>2603</v>
       </c>
       <c r="C2" t="n">
-        <v>3283</v>
+        <v>6993</v>
       </c>
       <c r="D2" t="n">
-        <v>3241</v>
+        <v>8891</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3972</v>
+        <v>826</v>
       </c>
       <c r="C2" t="n">
-        <v>5641</v>
+        <v>20959</v>
       </c>
       <c r="D2" t="n">
-        <v>9172</v>
+        <v>16464</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4663</v>
+        <v>297</v>
       </c>
       <c r="C3" t="n">
-        <v>5361</v>
+        <v>5520</v>
       </c>
       <c r="D3" t="n">
-        <v>12500</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5010</v>
+        <v>331</v>
       </c>
       <c r="C4" t="n">
-        <v>8520</v>
+        <v>4062</v>
       </c>
       <c r="D4" t="n">
-        <v>11445</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>520</v>
       </c>
       <c r="C5" t="n">
-        <v>11253</v>
+        <v>5158</v>
       </c>
       <c r="D5" t="n">
-        <v>5815</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>633</v>
+        <v>514</v>
       </c>
       <c r="C6" t="n">
-        <v>7115</v>
+        <v>5916</v>
       </c>
       <c r="D6" t="n">
-        <v>1934</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>2738</v>
+        <v>5925</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>914</v>
+        <v>4262</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>1992</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>666</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8090</v>
+        <v>3736</v>
       </c>
       <c r="C2" t="n">
-        <v>5773</v>
+        <v>15058</v>
       </c>
       <c r="D2" t="n">
-        <v>25803</v>
+        <v>17102</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3474</v>
+        <v>862</v>
       </c>
       <c r="C3" t="n">
-        <v>1680</v>
+        <v>2761</v>
       </c>
       <c r="D3" t="n">
-        <v>1209</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6155</v>
+        <v>2028</v>
       </c>
       <c r="C2" t="n">
-        <v>4551</v>
+        <v>6519</v>
       </c>
       <c r="D2" t="n">
-        <v>26387</v>
+        <v>16271</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4751</v>
+        <v>1951</v>
       </c>
       <c r="C3" t="n">
-        <v>3446</v>
+        <v>8757</v>
       </c>
       <c r="D3" t="n">
-        <v>5251</v>
+        <v>4382</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1543</v>
+        <v>426</v>
       </c>
       <c r="C4" t="n">
-        <v>1028</v>
+        <v>1770</v>
       </c>
       <c r="D4" t="n">
-        <v>1424</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6047</v>
+        <v>2634</v>
       </c>
       <c r="C2" t="n">
-        <v>4953</v>
+        <v>4437</v>
       </c>
       <c r="D2" t="n">
-        <v>20670</v>
+        <v>13887</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4477</v>
+        <v>1641</v>
       </c>
       <c r="C3" t="n">
-        <v>3504</v>
+        <v>6427</v>
       </c>
       <c r="D3" t="n">
-        <v>8254</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2667</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="n">
-        <v>2376</v>
+        <v>5891</v>
       </c>
       <c r="D4" t="n">
-        <v>2115</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>692</v>
+        <v>228</v>
       </c>
       <c r="C5" t="n">
-        <v>657</v>
+        <v>1102</v>
       </c>
       <c r="D5" t="n">
-        <v>1181</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8602</v>
+        <v>3050</v>
       </c>
       <c r="C2" t="n">
-        <v>8854</v>
+        <v>6718</v>
       </c>
       <c r="D2" t="n">
-        <v>19158</v>
+        <v>13155</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4295</v>
+        <v>1752</v>
       </c>
       <c r="C3" t="n">
-        <v>3699</v>
+        <v>4597</v>
       </c>
       <c r="D3" t="n">
-        <v>9560</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3042</v>
+        <v>1162</v>
       </c>
       <c r="C4" t="n">
-        <v>2910</v>
+        <v>6077</v>
       </c>
       <c r="D4" t="n">
-        <v>3150</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1380</v>
+        <v>541</v>
       </c>
       <c r="C5" t="n">
-        <v>1550</v>
+        <v>3745</v>
       </c>
       <c r="D5" t="n">
-        <v>1315</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>359</v>
+        <v>153</v>
       </c>
       <c r="C6" t="n">
-        <v>478</v>
+        <v>710</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10107</v>
+        <v>2612</v>
       </c>
       <c r="C2" t="n">
-        <v>14499</v>
+        <v>11044</v>
       </c>
       <c r="D2" t="n">
-        <v>22871</v>
+        <v>19363</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4694</v>
+        <v>1937</v>
       </c>
       <c r="C3" t="n">
-        <v>5188</v>
+        <v>4951</v>
       </c>
       <c r="D3" t="n">
-        <v>9734</v>
+        <v>7343</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2263</v>
+        <v>1246</v>
       </c>
       <c r="C4" t="n">
-        <v>2718</v>
+        <v>5096</v>
       </c>
       <c r="D4" t="n">
-        <v>3659</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1153</v>
+        <v>725</v>
       </c>
       <c r="C5" t="n">
-        <v>1659</v>
+        <v>4898</v>
       </c>
       <c r="D5" t="n">
-        <v>1305</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>414</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>682</v>
+        <v>2246</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>265</v>
+        <v>501</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8464</v>
+        <v>2696</v>
       </c>
       <c r="C2" t="n">
-        <v>8620</v>
+        <v>7752</v>
       </c>
       <c r="D2" t="n">
-        <v>21153</v>
+        <v>24954</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6165</v>
+        <v>1843</v>
       </c>
       <c r="C3" t="n">
-        <v>9216</v>
+        <v>6916</v>
       </c>
       <c r="D3" t="n">
-        <v>11314</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3064</v>
+        <v>1331</v>
       </c>
       <c r="C4" t="n">
-        <v>4179</v>
+        <v>4916</v>
       </c>
       <c r="D4" t="n">
-        <v>4830</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1516</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>2254</v>
+        <v>4893</v>
       </c>
       <c r="D5" t="n">
-        <v>1739</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>731</v>
+        <v>441</v>
       </c>
       <c r="C6" t="n">
-        <v>1236</v>
+        <v>3448</v>
       </c>
       <c r="D6" t="n">
-        <v>851</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>501</v>
+        <v>1321</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6527</v>
+        <v>2455</v>
       </c>
       <c r="C2" t="n">
-        <v>5972</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="n">
-        <v>32179</v>
+        <v>19528</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5996</v>
+        <v>2405</v>
       </c>
       <c r="C3" t="n">
-        <v>7696</v>
+        <v>9717</v>
       </c>
       <c r="D3" t="n">
-        <v>12073</v>
+        <v>9764</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3931</v>
+        <v>786</v>
       </c>
       <c r="C4" t="n">
-        <v>6945</v>
+        <v>7764</v>
       </c>
       <c r="D4" t="n">
-        <v>5928</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>3238</v>
+        <v>3379</v>
       </c>
       <c r="D5" t="n">
-        <v>2233</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1015</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>1768</v>
+        <v>1294</v>
       </c>
       <c r="D6" t="n">
-        <v>1001</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>889</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
